--- a/arquivos/Materiais e aplicações.xlsx
+++ b/arquivos/Materiais e aplicações.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="524">
   <si>
     <t xml:space="preserve">Categoria</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t xml:space="preserve">Grau de Dificuldade de Aplicação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durabilidade</t>
   </si>
   <si>
     <t xml:space="preserve">Arquitetura / Decorativo</t>
@@ -1696,7 +1699,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1889,7 +1892,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.71"/>
@@ -1901,7 +1904,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="118.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="29.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="10" style="1" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="11" style="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1932,89 +1936,98 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>1.1</v>
       </c>
+      <c r="J2" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>1.1</v>
       </c>
+      <c r="J3" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>1.1</v>
@@ -2022,28 +2035,28 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1</v>
@@ -2051,28 +2064,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.1</v>
@@ -2080,28 +2093,28 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.1</v>
@@ -2109,28 +2122,28 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>1.1</v>
@@ -2138,28 +2151,28 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>1</v>
@@ -2167,28 +2180,28 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.1</v>
@@ -2196,28 +2209,28 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>1.3</v>
@@ -2225,28 +2238,28 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>1.3</v>
@@ -2254,28 +2267,28 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.3</v>
@@ -2283,28 +2296,28 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.3</v>
@@ -2312,28 +2325,28 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>1.3</v>
@@ -2341,28 +2354,28 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>1.3</v>
@@ -2370,28 +2383,28 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>1.3</v>
@@ -2399,28 +2412,28 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>1.3</v>
@@ -2428,28 +2441,28 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>22.86</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.3</v>
@@ -2457,28 +2470,28 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>22.86</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.3</v>
@@ -2486,28 +2499,28 @@
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1.3</v>
@@ -2515,28 +2528,28 @@
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>1.3</v>
@@ -2544,28 +2557,28 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1.3</v>
@@ -2573,28 +2586,28 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.3</v>
@@ -2602,28 +2615,28 @@
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1.3</v>
@@ -2631,28 +2644,28 @@
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.3</v>
@@ -2660,28 +2673,28 @@
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.3</v>
@@ -2689,28 +2702,28 @@
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>1.3</v>
@@ -2718,28 +2731,28 @@
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.3</v>
@@ -2747,28 +2760,28 @@
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>1.3</v>
@@ -2776,28 +2789,28 @@
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>22.86</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1.3</v>
@@ -2805,28 +2818,28 @@
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
@@ -2834,28 +2847,28 @@
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>1.3</v>
@@ -2863,28 +2876,28 @@
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.3</v>
@@ -2892,28 +2905,28 @@
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>1.3</v>
@@ -2921,28 +2934,28 @@
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.2</v>
@@ -2950,28 +2963,28 @@
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>1.3</v>
@@ -2979,28 +2992,28 @@
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>22.86</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>1.3</v>
@@ -3008,28 +3021,28 @@
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>1.3</v>
@@ -3037,28 +3050,28 @@
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>1.3</v>
@@ -3066,28 +3079,28 @@
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F41" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>1.3</v>
@@ -3095,28 +3108,28 @@
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F42" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>1.2</v>
@@ -3124,28 +3137,28 @@
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>1.3</v>
@@ -3153,28 +3166,28 @@
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F44" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.3</v>
@@ -3182,28 +3195,28 @@
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>1.3</v>
@@ -3211,28 +3224,28 @@
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>1.3</v>
@@ -3240,28 +3253,28 @@
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>1.3</v>
@@ -3269,28 +3282,28 @@
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>1.3</v>
@@ -3298,28 +3311,28 @@
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>1.3</v>
@@ -3327,28 +3340,28 @@
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>1.3</v>
@@ -3356,28 +3369,28 @@
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>1.3</v>
@@ -3385,28 +3398,28 @@
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>1.3</v>
@@ -3414,28 +3427,28 @@
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I53" s="3" t="n">
         <v>1.3</v>
@@ -3443,28 +3456,28 @@
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="H54" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>1.3</v>
@@ -3472,28 +3485,28 @@
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F55" s="4" t="n">
         <v>22.86</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>1.3</v>
@@ -3501,28 +3514,28 @@
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F56" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>1.3</v>
@@ -3530,28 +3543,28 @@
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F57" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>1.2</v>
@@ -3559,28 +3572,28 @@
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>1.3</v>
@@ -3588,28 +3601,28 @@
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F59" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>1.3</v>
@@ -3617,28 +3630,28 @@
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F60" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>1.2</v>
@@ -3646,28 +3659,28 @@
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H61" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F61" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>1.2</v>
@@ -3675,28 +3688,28 @@
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>1.3</v>
@@ -3704,28 +3717,28 @@
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F63" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>1.3</v>
@@ -3733,28 +3746,28 @@
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F64" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>1.3</v>
@@ -3762,28 +3775,28 @@
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F65" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>1.3</v>
@@ -3791,28 +3804,28 @@
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F66" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>1.3</v>
@@ -3820,28 +3833,28 @@
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F67" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>1.2</v>
@@ -3849,28 +3862,28 @@
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F68" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>1.3</v>
@@ -3878,28 +3891,28 @@
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F69" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>1.2</v>
@@ -3907,28 +3920,28 @@
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F70" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>1.3</v>
@@ -3936,28 +3949,28 @@
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F71" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>1.3</v>
@@ -3965,28 +3978,28 @@
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F72" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>1.2</v>
@@ -3994,28 +4007,28 @@
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F73" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>1.3</v>
@@ -4023,28 +4036,28 @@
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F74" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>1.3</v>
@@ -4052,28 +4065,28 @@
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F75" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>1.1</v>
@@ -4081,28 +4094,28 @@
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>1.2</v>
@@ -4110,28 +4123,28 @@
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F77" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I77" s="3" t="n">
         <v>1.1</v>
@@ -4139,28 +4152,28 @@
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G78" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="H78" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>1.1</v>
@@ -4168,28 +4181,28 @@
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="E79" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F79" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>1.1</v>
@@ -4197,28 +4210,28 @@
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F80" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>1.1</v>
@@ -4226,28 +4239,28 @@
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F81" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I81" s="3" t="n">
         <v>1.1</v>
@@ -4255,28 +4268,28 @@
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F82" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>1.3</v>
@@ -4284,28 +4297,28 @@
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F83" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>1.3</v>
@@ -4313,28 +4326,28 @@
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F84" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>1.1</v>
@@ -4342,28 +4355,28 @@
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F85" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>1.3</v>
@@ -4371,28 +4384,28 @@
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F86" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>1.3</v>
@@ -4400,28 +4413,28 @@
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F87" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I87" s="3" t="n">
         <v>1.3</v>
@@ -4429,28 +4442,28 @@
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F88" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>1.3</v>
@@ -4458,28 +4471,28 @@
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F89" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I89" s="3" t="n">
         <v>1.3</v>
@@ -4487,28 +4500,28 @@
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F90" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>1.1</v>
@@ -4516,28 +4529,28 @@
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F91" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>1.1</v>
@@ -4545,28 +4558,28 @@
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F92" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>1.1</v>
@@ -4574,28 +4587,28 @@
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>1.1</v>
@@ -4603,28 +4616,28 @@
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>1.1</v>
@@ -4632,28 +4645,28 @@
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>1.1</v>
@@ -4661,28 +4674,28 @@
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F96" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>1.3</v>
@@ -4690,28 +4703,28 @@
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F97" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>1.1</v>
@@ -4719,28 +4732,28 @@
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F98" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>1.1</v>
@@ -4748,28 +4761,28 @@
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F99" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>1</v>
@@ -4777,28 +4790,28 @@
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F100" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>1</v>
@@ -4806,28 +4819,28 @@
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F101" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>1</v>
@@ -4835,28 +4848,28 @@
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F102" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>1</v>
@@ -4864,28 +4877,28 @@
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F103" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>1</v>
@@ -4893,28 +4906,28 @@
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F104" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>1</v>
@@ -4922,28 +4935,28 @@
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F105" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I105" s="3" t="n">
         <v>1</v>
@@ -4951,28 +4964,28 @@
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F106" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>1</v>
@@ -4980,28 +4993,28 @@
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F107" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>1.1</v>
@@ -5009,28 +5022,28 @@
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F108" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>1.1</v>
@@ -5038,28 +5051,28 @@
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I109" s="3" t="n">
         <v>1.1</v>
@@ -5067,28 +5080,28 @@
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F110" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>1.1</v>
@@ -5096,28 +5109,28 @@
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>1.1</v>
@@ -5125,28 +5138,28 @@
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F112" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>1.1</v>
@@ -5154,28 +5167,28 @@
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F113" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I113" s="3" t="n">
         <v>1.1</v>
@@ -5183,28 +5196,28 @@
     </row>
     <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F114" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>1.1</v>
@@ -5212,28 +5225,28 @@
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F115" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>1.1</v>
@@ -5241,28 +5254,28 @@
     </row>
     <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F116" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>1.1</v>
@@ -5270,28 +5283,28 @@
     </row>
     <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F117" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>1.1</v>
@@ -5299,28 +5312,28 @@
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F118" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>1.1</v>
@@ -5328,28 +5341,28 @@
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F119" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I119" s="3" t="n">
         <v>1.1</v>
@@ -5357,28 +5370,28 @@
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F120" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>1.1</v>
@@ -5386,28 +5399,28 @@
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F121" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>1.1</v>
@@ -5415,28 +5428,28 @@
     </row>
     <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F122" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>1.1</v>
@@ -5444,28 +5457,28 @@
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F123" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>1.1</v>
@@ -5473,28 +5486,28 @@
     </row>
     <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F124" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>1.1</v>
@@ -5502,28 +5515,28 @@
     </row>
     <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>1.1</v>
@@ -5531,28 +5544,28 @@
     </row>
     <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="H126" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>1.1</v>
@@ -5560,28 +5573,28 @@
     </row>
     <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H127" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="I127" s="3" t="n">
         <v>1.1</v>
@@ -5589,28 +5602,28 @@
     </row>
     <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="H128" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G128" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>1.1</v>
@@ -5618,28 +5631,28 @@
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="H129" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H129" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>1.1</v>
@@ -5647,28 +5660,28 @@
     </row>
     <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="H130" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="H130" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="I130" s="3" t="n">
         <v>1.1</v>
@@ -5676,28 +5689,28 @@
     </row>
     <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H131" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G131" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H131" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="I131" s="3" t="n">
         <v>1.1</v>
@@ -5705,28 +5718,28 @@
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F132" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>1.1</v>
@@ -5734,28 +5747,28 @@
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F133" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I133" s="3" t="n">
         <v>1.2</v>
@@ -5763,28 +5776,28 @@
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F134" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>1.1</v>
@@ -5792,28 +5805,28 @@
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F135" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>1.1</v>
@@ -5821,28 +5834,28 @@
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F136" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>1.3</v>
@@ -5850,28 +5863,28 @@
     </row>
     <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F137" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I137" s="3" t="n">
         <v>1.1</v>
@@ -5879,28 +5892,28 @@
     </row>
     <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F138" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I138" s="3" t="n">
         <v>1.1</v>
@@ -5908,28 +5921,28 @@
     </row>
     <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F139" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I139" s="3" t="n">
         <v>1.1</v>
@@ -5937,28 +5950,28 @@
     </row>
     <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F140" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I140" s="3" t="n">
         <v>1.1</v>
@@ -5966,28 +5979,28 @@
     </row>
     <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F141" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I141" s="3" t="n">
         <v>1.3</v>
@@ -5995,28 +6008,28 @@
     </row>
     <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F142" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>1.3</v>
@@ -6024,28 +6037,28 @@
     </row>
     <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F143" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I143" s="3" t="n">
         <v>1.2</v>
@@ -6053,28 +6066,28 @@
     </row>
     <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F144" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I144" s="3" t="n">
         <v>1.1</v>
@@ -6082,28 +6095,28 @@
     </row>
     <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F145" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I145" s="3" t="n">
         <v>1.1</v>
@@ -6111,28 +6124,28 @@
     </row>
     <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F146" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>1.1</v>
@@ -6140,28 +6153,28 @@
     </row>
     <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F147" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I147" s="3" t="n">
         <v>1.1</v>
@@ -6169,28 +6182,28 @@
     </row>
     <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F148" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I148" s="3" t="n">
         <v>1.1</v>
@@ -6198,28 +6211,28 @@
     </row>
     <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F149" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I149" s="3" t="n">
         <v>1.1</v>
@@ -6227,28 +6240,28 @@
     </row>
     <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F150" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>1.3</v>
@@ -6256,28 +6269,28 @@
     </row>
     <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F151" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I151" s="3" t="n">
         <v>1</v>
@@ -6285,28 +6298,28 @@
     </row>
     <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F152" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I152" s="3" t="n">
         <v>1</v>
@@ -6314,28 +6327,28 @@
     </row>
     <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F153" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I153" s="3" t="n">
         <v>1</v>
@@ -6343,28 +6356,28 @@
     </row>
     <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F154" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>1.3</v>
@@ -6372,28 +6385,28 @@
     </row>
     <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F155" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I155" s="3" t="n">
         <v>1.3</v>
@@ -6401,28 +6414,28 @@
     </row>
     <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F156" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>1.2</v>
@@ -6430,28 +6443,28 @@
     </row>
     <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F157" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I157" s="3" t="n">
         <v>1.2</v>
@@ -6459,28 +6472,28 @@
     </row>
     <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F158" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>1.3</v>
@@ -6488,28 +6501,28 @@
     </row>
     <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F159" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I159" s="3" t="n">
         <v>1.3</v>
@@ -6517,28 +6530,28 @@
     </row>
     <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F160" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>1.3</v>
@@ -6546,28 +6559,28 @@
     </row>
     <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F161" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I161" s="3" t="n">
         <v>1.1</v>
@@ -6575,28 +6588,28 @@
     </row>
     <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F162" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>1.1</v>
@@ -6604,28 +6617,28 @@
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F163" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I163" s="3" t="n">
         <v>1.1</v>
@@ -6633,28 +6646,28 @@
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F164" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>1.1</v>
@@ -6662,28 +6675,28 @@
     </row>
     <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F165" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I165" s="3" t="n">
         <v>1.3</v>
@@ -6691,28 +6704,28 @@
     </row>
     <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F166" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>1.3</v>
@@ -6720,28 +6733,28 @@
     </row>
     <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F167" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I167" s="3" t="n">
         <v>1.3</v>
@@ -6749,28 +6762,28 @@
     </row>
     <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F168" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>1.3</v>
@@ -6778,28 +6791,28 @@
     </row>
     <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F169" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I169" s="3" t="n">
         <v>1.3</v>
@@ -6807,28 +6820,28 @@
     </row>
     <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F170" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>1.3</v>
@@ -6836,28 +6849,28 @@
     </row>
     <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F171" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I171" s="3" t="n">
         <v>1.3</v>
@@ -6865,28 +6878,28 @@
     </row>
     <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F172" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>1.2</v>
@@ -6894,28 +6907,28 @@
     </row>
     <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F173" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I173" s="3" t="n">
         <v>1.3</v>
@@ -6923,28 +6936,28 @@
     </row>
     <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F174" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>1.3</v>
@@ -6952,28 +6965,28 @@
     </row>
     <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F175" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I175" s="3" t="n">
         <v>1.3</v>
@@ -6981,28 +6994,28 @@
     </row>
     <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F176" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>1.3</v>
@@ -7010,28 +7023,28 @@
     </row>
     <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F177" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I177" s="3" t="n">
         <v>1.3</v>
@@ -7039,28 +7052,28 @@
     </row>
     <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F178" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>1.3</v>
@@ -7068,28 +7081,28 @@
     </row>
     <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F179" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I179" s="3" t="n">
         <v>1.3</v>
@@ -7097,28 +7110,28 @@
     </row>
     <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F180" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>1.3</v>
@@ -7126,28 +7139,28 @@
     </row>
     <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F181" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I181" s="3" t="n">
         <v>1.3</v>
@@ -7155,28 +7168,28 @@
     </row>
     <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F182" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I182" s="3" t="n">
         <v>1.1</v>
@@ -7184,28 +7197,28 @@
     </row>
     <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C183" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="H183" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="D183" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="E183" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="F183" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G183" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="H183" s="3" t="s">
-        <v>483</v>
       </c>
       <c r="I183" s="3" t="n">
         <v>1.1</v>
@@ -7213,28 +7226,28 @@
     </row>
     <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F184" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I184" s="3" t="n">
         <v>1.1</v>
@@ -7242,28 +7255,28 @@
     </row>
     <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F185" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I185" s="3" t="n">
         <v>1.1</v>
@@ -7271,28 +7284,28 @@
     </row>
     <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F186" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I186" s="3" t="n">
         <v>1.1</v>
@@ -7300,28 +7313,28 @@
     </row>
     <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F187" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I187" s="3" t="n">
         <v>1.1</v>
@@ -7329,28 +7342,28 @@
     </row>
     <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C188" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F188" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G188" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="D188" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="E188" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F188" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>498</v>
-      </c>
       <c r="H188" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>1.1</v>
@@ -7358,28 +7371,28 @@
     </row>
     <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F189" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I189" s="3" t="n">
         <v>1.1</v>
@@ -7387,28 +7400,28 @@
     </row>
     <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C190" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F190" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="H190" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="E190" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F190" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G190" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="H190" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="I190" s="3" t="n">
         <v>1.1</v>
@@ -7416,28 +7429,28 @@
     </row>
     <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F191" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I191" s="3" t="n">
         <v>1.1</v>
@@ -7445,28 +7458,28 @@
     </row>
     <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D192" s="3" t="n">
         <v>45</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F192" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>1.1</v>
@@ -7474,28 +7487,28 @@
     </row>
     <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D193" s="3" t="n">
         <v>42</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F193" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I193" s="3" t="n">
         <v>1.1</v>
@@ -7503,28 +7516,28 @@
     </row>
     <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D194" s="3" t="n">
         <v>42</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F194" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>1.1</v>
@@ -7532,28 +7545,28 @@
     </row>
     <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F195" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I195" s="3" t="n">
         <v>1.3</v>
